--- a/pages/shp/uploads/27-10-2025 - 27-10-2025.xlsx
+++ b/pages/shp/uploads/27-10-2025 - 27-10-2025.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="327">
   <si>
     <t>NOMOR AJU</t>
   </si>
@@ -347,13 +347,10 @@
     <t>FLAG PROPORSIONAL NETTO</t>
   </si>
   <si>
-    <t>00003074540620251027001594</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>040300</t>
+    <t>00004174540620251027002211</t>
+  </si>
+  <si>
+    <t>41</t>
   </si>
   <si>
     <t>050500</t>
@@ -362,482 +359,468 @@
     <t>1</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>41</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>BANDUNG</t>
+  </si>
+  <si>
+    <t>2025-10-27</t>
+  </si>
+  <si>
+    <t>YUS YULIUS</t>
+  </si>
+  <si>
+    <t>EXIM MANAGER</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>019542</t>
+  </si>
+  <si>
+    <t>00004174540620251027002212</t>
+  </si>
+  <si>
+    <t>019555</t>
+  </si>
+  <si>
+    <t>KODE FASILITAS TARIF</t>
+  </si>
+  <si>
+    <t>KODE JENIS PUNGUTAN</t>
+  </si>
+  <si>
+    <t>NILAI PUNGUTAN</t>
+  </si>
+  <si>
+    <t>NPWP BILLING</t>
+  </si>
+  <si>
+    <t>SERI</t>
+  </si>
+  <si>
+    <t>KODE ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS IDENTITAS</t>
+  </si>
+  <si>
+    <t>NOMOR IDENTITAS</t>
+  </si>
+  <si>
+    <t>NAMA ENTITAS</t>
+  </si>
+  <si>
+    <t>ALAMAT ENTITAS</t>
+  </si>
+  <si>
+    <t>NIB ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE JENIS API</t>
+  </si>
+  <si>
+    <t>KODE STATUS</t>
+  </si>
+  <si>
+    <t>NOMOR IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>TANGGAL IJIN ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE NEGARA</t>
+  </si>
+  <si>
+    <t>NIPER ENTITAS</t>
+  </si>
+  <si>
+    <t>KODE KATEGORI KONSOLIDATOR</t>
+  </si>
+  <si>
+    <t>KODE AFILIASI</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>US</t>
-  </si>
-  <si>
-    <t>IDTPP</t>
-  </si>
-  <si>
-    <t>USNYC</t>
-  </si>
-  <si>
-    <t>2025-11-03</t>
-  </si>
-  <si>
-    <t>2025-10-27</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>DN</t>
-  </si>
-  <si>
-    <t>BANDUNG</t>
-  </si>
-  <si>
-    <t>YUS YULIUS</t>
-  </si>
-  <si>
-    <t>MANAGER EXIM</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>EXW</t>
-  </si>
-  <si>
-    <t>670931</t>
+    <t>0745406926444000000000</t>
+  </si>
+  <si>
+    <t>NIRWANA ALABARE GARMENT</t>
+  </si>
+  <si>
+    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 SOLOKANJERUK SOLOKANJERUK KAB. BANDUNG JAWA BARAT</t>
+  </si>
+  <si>
+    <t>0220103231143</t>
+  </si>
+  <si>
+    <t>258/KM.4/WBC.09/2024</t>
+  </si>
+  <si>
+    <t>12-11-2024 00:00:00</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>0954918173425000000000</t>
+  </si>
+  <si>
+    <t>LOZY</t>
+  </si>
+  <si>
+    <t>KAMPUNG CIAWI PANUNGGAL   002 006 CIPEDES CIPEDES KOTA TASIKMALAYA JAWA BARAT</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>LAINNYA</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>JALAN RAYA RANCAEKAEK MAJALAYA NO.289 001/007 SOLOKANJERUK, SOLOKANJERUK, BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>0631648888428000000000</t>
+  </si>
+  <si>
+    <t>CIPTA BUSANA UTAMA</t>
+  </si>
+  <si>
+    <t>KOMODOR UDARA SUPADIO NO.15 RT.001 RW.005, HUSEIN SASTRANEGARA, CICENDO, KOTA BANDUNG, JAWA BARAT</t>
+  </si>
+  <si>
+    <t>NOMOR DOKUMEN</t>
+  </si>
+  <si>
+    <t>TANGGAL DOKUMEN</t>
+  </si>
+  <si>
+    <t>KODE FASILITAS</t>
+  </si>
+  <si>
+    <t>KODE IJIN</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>GK/RO/1025/00636,00637,00640</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>001/LOZY/KK/061025</t>
+  </si>
+  <si>
+    <t>2025-10-06</t>
+  </si>
+  <si>
+    <t>03054</t>
+  </si>
+  <si>
+    <t>S-327/KBC.0903//KBC.090313/2025</t>
+  </si>
+  <si>
+    <t>2025-10-07</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>117290</t>
+  </si>
+  <si>
+    <t>2025-10-23</t>
+  </si>
+  <si>
+    <t>S-2011/KBC.0903/2025</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>118507</t>
+  </si>
+  <si>
+    <t>2025-10-25</t>
+  </si>
+  <si>
+    <t>S-313/KBC.0903/KBC.090313/2025</t>
+  </si>
+  <si>
+    <t>2025-08-20</t>
+  </si>
+  <si>
+    <t>NO.I/LEG.VEN/VII/25</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>0669,0670,671,672,673,674,675,676,677,678,679/L/NAG/1025</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>113661</t>
+  </si>
+  <si>
+    <t>2025-10-14</t>
+  </si>
+  <si>
+    <t>KODE CARA ANGKUT</t>
+  </si>
+  <si>
+    <t>NAMA PENGANGKUT</t>
+  </si>
+  <si>
+    <t>NOMOR PENGANGKUT</t>
+  </si>
+  <si>
+    <t>KODE BENDERA</t>
+  </si>
+  <si>
+    <t>CALL SIGN</t>
+  </si>
+  <si>
+    <t>FLAG ANGKUT PLB</t>
+  </si>
+  <si>
+    <t>CARA PENGANGKUTAN LAINNYA</t>
+  </si>
+  <si>
+    <t>MOBIL</t>
+  </si>
+  <si>
+    <t>KODE KEMASAN</t>
+  </si>
+  <si>
+    <t>JUMLAH KEMASAN</t>
+  </si>
+  <si>
+    <t>MEREK</t>
+  </si>
+  <si>
+    <t>RO</t>
+  </si>
+  <si>
+    <t>PK</t>
+  </si>
+  <si>
+    <t>NOMOR KONTINER</t>
+  </si>
+  <si>
+    <t>KODE UKURAN KONTAINER</t>
+  </si>
+  <si>
+    <t>KODE JENIS KONTAINER</t>
+  </si>
+  <si>
+    <t>KODE TIPE KONTAINER</t>
+  </si>
+  <si>
+    <t>SERI BARANG</t>
+  </si>
+  <si>
+    <t>HS</t>
+  </si>
+  <si>
+    <t>KODE BARANG</t>
+  </si>
+  <si>
+    <t>URAIAN</t>
+  </si>
+  <si>
+    <t>TIPE</t>
+  </si>
+  <si>
+    <t>UKURAN</t>
+  </si>
+  <si>
+    <t>SPESIFIKASI LAIN</t>
+  </si>
+  <si>
+    <t>KODE SATUAN</t>
+  </si>
+  <si>
+    <t>JUMLAH SATUAN</t>
+  </si>
+  <si>
+    <t>KODE DOKUMEN ASAL</t>
+  </si>
+  <si>
+    <t>KODE KANTOR ASAL</t>
+  </si>
+  <si>
+    <t>NOMOR DAFTAR ASAL</t>
+  </si>
+  <si>
+    <t>TANGGAL DAFTAR ASAL</t>
+  </si>
+  <si>
+    <t>NOMOR AJU ASAL</t>
+  </si>
+  <si>
+    <t>SERI BARANG ASAL</t>
+  </si>
+  <si>
+    <t>SALDO AWAL</t>
+  </si>
+  <si>
+    <t>SALDO AKHIR</t>
+  </si>
+  <si>
+    <t>JUMLAH REALISASI</t>
+  </si>
+  <si>
+    <t>CIF RUPIAH</t>
+  </si>
+  <si>
+    <t>NILAI TAMBAH</t>
+  </si>
+  <si>
+    <t>DISKON</t>
+  </si>
+  <si>
+    <t>HARGA PENYERAHAN</t>
+  </si>
+  <si>
+    <t>HARGA PEROLEHAN</t>
+  </si>
+  <si>
+    <t>HARGA SATUAN</t>
+  </si>
+  <si>
+    <t>HARGA EKSPOR</t>
+  </si>
+  <si>
+    <t>HARGA PATOKAN</t>
+  </si>
+  <si>
+    <t>NILAI DANA SAWIT</t>
+  </si>
+  <si>
+    <t>NILAI DEVISA</t>
+  </si>
+  <si>
+    <t>PERSENTASE IMPOR</t>
+  </si>
+  <si>
+    <t>KODE ASAL BARANG</t>
+  </si>
+  <si>
+    <t>KODE GUNA BARANG</t>
+  </si>
+  <si>
+    <t>JATUH TEMPO ROYALTI</t>
+  </si>
+  <si>
+    <t>KODE KATEGORI BARANG</t>
+  </si>
+  <si>
+    <t>KODE KONDISI BARANG</t>
+  </si>
+  <si>
+    <t>KODE NEGARA ASAL</t>
+  </si>
+  <si>
+    <t>KODE PERHITUNGAN</t>
+  </si>
+  <si>
+    <t>PERNYATAAN LARTAS</t>
+  </si>
+  <si>
+    <t>FLAG 4 TAHUN</t>
+  </si>
+  <si>
+    <t>SERI IZIN</t>
+  </si>
+  <si>
+    <t>TAHUN PEMBUATAN</t>
+  </si>
+  <si>
+    <t>KAPASITAS SILINDER</t>
+  </si>
+  <si>
+    <t>KODE BKC</t>
+  </si>
+  <si>
+    <t>KODE KOMODITI BKC</t>
+  </si>
+  <si>
+    <t>KODE SUB KOMODITI BKC</t>
+  </si>
+  <si>
+    <t>FLAG TIS</t>
+  </si>
+  <si>
+    <t>ISI PER KEMASAN</t>
+  </si>
+  <si>
+    <t>JUMLAH DILEKATKAN</t>
+  </si>
+  <si>
+    <t>JUMLAH PITA CUKAI</t>
+  </si>
+  <si>
+    <t>HJE CUKAI</t>
+  </si>
+  <si>
+    <t>TARIF CUKAI</t>
+  </si>
+  <si>
+    <t>METODE PENENTUAN NILAI</t>
+  </si>
+  <si>
+    <t>ALASAN METODE PENENTUAN NILAI</t>
+  </si>
+  <si>
+    <t>STATEMENT PERBEDAAN HARGA</t>
+  </si>
+  <si>
+    <t>55161200</t>
+  </si>
+  <si>
+    <t>2938</t>
+  </si>
+  <si>
+    <t>FABRIC KNIT SJ RY 401 COMPACT TUBULAR (RETUR)</t>
+  </si>
+  <si>
+    <t>KGM</t>
   </si>
   <si>
     <t>T</t>
   </si>
   <si>
-    <t>00003074540620251027001595</t>
-  </si>
-  <si>
-    <t>671073</t>
-  </si>
-  <si>
-    <t>KODE FASILITAS TARIF</t>
-  </si>
-  <si>
-    <t>KODE JENIS PUNGUTAN</t>
-  </si>
-  <si>
-    <t>NILAI PUNGUTAN</t>
-  </si>
-  <si>
-    <t>NPWP BILLING</t>
-  </si>
-  <si>
-    <t>SERI</t>
-  </si>
-  <si>
-    <t>KODE ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS IDENTITAS</t>
-  </si>
-  <si>
-    <t>NOMOR IDENTITAS</t>
-  </si>
-  <si>
-    <t>NAMA ENTITAS</t>
-  </si>
-  <si>
-    <t>ALAMAT ENTITAS</t>
-  </si>
-  <si>
-    <t>NIB ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE JENIS API</t>
-  </si>
-  <si>
-    <t>KODE STATUS</t>
-  </si>
-  <si>
-    <t>NOMOR IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>TANGGAL IJIN ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE NEGARA</t>
-  </si>
-  <si>
-    <t>NIPER ENTITAS</t>
-  </si>
-  <si>
-    <t>KODE KATEGORI KONSOLIDATOR</t>
-  </si>
-  <si>
-    <t>KODE AFILIASI</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>000000000000000</t>
-  </si>
-  <si>
-    <t>KANMAX ENTERPRISES LTD</t>
-  </si>
-  <si>
-    <t>60 PAYA LEBAR ROAD #04-21 PAYA LEBAR SQUARE 409051 SINGAPORE</t>
-  </si>
-  <si>
-    <t>OLD NAVY, LLC</t>
-  </si>
-  <si>
-    <t>2 FOLSOM STREET
-SAN FRANCISCO, CALIFORNIA
-94105</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>FISHKILL NY ONLINE-0007</t>
-  </si>
-  <si>
-    <t>110 MERRITT BLVD
-FISHKILL, NY
-12524</t>
-  </si>
-  <si>
-    <t>0745406926444000000000</t>
-  </si>
-  <si>
-    <t>NIRWANA ALABARE GARMENT</t>
-  </si>
-  <si>
-    <t>JL RAYA RANCAEKEK MAJALAYA NO.289 RT.002 RW.007, SOLOKANJERUK, SOLOKANJERUK, KABUPATEN BANDUNG, JAWA BARAT</t>
-  </si>
-  <si>
-    <t>0220103231143</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>0926856451045000000000</t>
-  </si>
-  <si>
-    <t>KBN PRIMA LOGISTIK</t>
-  </si>
-  <si>
-    <t>GEDUNG MAWAR, JALAN RAYA CAKUNG CILINCING, TANJUNG PRIOK000000   SUKAPURA CILINCING KOTA ADM. JAKARTA UTARA DKI JAKARTA</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>LAINNYA</t>
-  </si>
-  <si>
-    <t>OHO OHIO OMNI-0016</t>
-  </si>
-  <si>
-    <t>6001 GREEN POINTE DR S
-GROVEPORT, OH
-43125</t>
-  </si>
-  <si>
-    <t>NOMOR DOKUMEN</t>
-  </si>
-  <si>
-    <t>TANGGAL DOKUMEN</t>
-  </si>
-  <si>
-    <t>KODE FASILITAS</t>
-  </si>
-  <si>
-    <t>KODE IJIN</t>
-  </si>
-  <si>
-    <t>920</t>
-  </si>
-  <si>
-    <t>258/KM.4/WBC.09/2024</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>0666ENAG1025</t>
-  </si>
-  <si>
-    <t>217</t>
-  </si>
-  <si>
-    <t>025269</t>
-  </si>
-  <si>
-    <t>2025-07-01</t>
-  </si>
-  <si>
-    <t>0667ENAG1025</t>
-  </si>
-  <si>
-    <t>KODE CARA ANGKUT</t>
-  </si>
-  <si>
-    <t>NAMA PENGANGKUT</t>
-  </si>
-  <si>
-    <t>NOMOR PENGANGKUT</t>
-  </si>
-  <si>
-    <t>KODE BENDERA</t>
-  </si>
-  <si>
-    <t>CALL SIGN</t>
-  </si>
-  <si>
-    <t>FLAG ANGKUT PLB</t>
-  </si>
-  <si>
-    <t>CARA PENGANGKUTAN LAINNYA</t>
-  </si>
-  <si>
-    <t>MERATUS TOMINI</t>
-  </si>
-  <si>
-    <t>VV 545N</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>KODE KEMASAN</t>
-  </si>
-  <si>
-    <t>JUMLAH KEMASAN</t>
-  </si>
-  <si>
-    <t>MEREK</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>OLD NAVY</t>
-  </si>
-  <si>
-    <t>NOMOR KONTINER</t>
-  </si>
-  <si>
-    <t>KODE UKURAN KONTAINER</t>
-  </si>
-  <si>
-    <t>KODE JENIS KONTAINER</t>
-  </si>
-  <si>
-    <t>KODE TIPE KONTAINER</t>
-  </si>
-  <si>
-    <t>SERI BARANG</t>
-  </si>
-  <si>
-    <t>HS</t>
-  </si>
-  <si>
-    <t>KODE BARANG</t>
-  </si>
-  <si>
-    <t>URAIAN</t>
-  </si>
-  <si>
-    <t>TIPE</t>
-  </si>
-  <si>
-    <t>UKURAN</t>
-  </si>
-  <si>
-    <t>SPESIFIKASI LAIN</t>
-  </si>
-  <si>
-    <t>KODE SATUAN</t>
-  </si>
-  <si>
-    <t>JUMLAH SATUAN</t>
-  </si>
-  <si>
-    <t>KODE DOKUMEN ASAL</t>
-  </si>
-  <si>
-    <t>KODE KANTOR ASAL</t>
-  </si>
-  <si>
-    <t>NOMOR DAFTAR ASAL</t>
-  </si>
-  <si>
-    <t>TANGGAL DAFTAR ASAL</t>
-  </si>
-  <si>
-    <t>NOMOR AJU ASAL</t>
-  </si>
-  <si>
-    <t>SERI BARANG ASAL</t>
-  </si>
-  <si>
-    <t>SALDO AWAL</t>
-  </si>
-  <si>
-    <t>SALDO AKHIR</t>
-  </si>
-  <si>
-    <t>JUMLAH REALISASI</t>
-  </si>
-  <si>
-    <t>CIF RUPIAH</t>
-  </si>
-  <si>
-    <t>NILAI TAMBAH</t>
-  </si>
-  <si>
-    <t>DISKON</t>
-  </si>
-  <si>
-    <t>HARGA PENYERAHAN</t>
-  </si>
-  <si>
-    <t>HARGA PEROLEHAN</t>
-  </si>
-  <si>
-    <t>HARGA SATUAN</t>
-  </si>
-  <si>
-    <t>HARGA EKSPOR</t>
-  </si>
-  <si>
-    <t>HARGA PATOKAN</t>
-  </si>
-  <si>
-    <t>NILAI DANA SAWIT</t>
-  </si>
-  <si>
-    <t>NILAI DEVISA</t>
-  </si>
-  <si>
-    <t>PERSENTASE IMPOR</t>
-  </si>
-  <si>
-    <t>KODE ASAL BARANG</t>
-  </si>
-  <si>
-    <t>KODE GUNA BARANG</t>
-  </si>
-  <si>
-    <t>JATUH TEMPO ROYALTI</t>
-  </si>
-  <si>
-    <t>KODE KATEGORI BARANG</t>
-  </si>
-  <si>
-    <t>KODE KONDISI BARANG</t>
-  </si>
-  <si>
-    <t>KODE NEGARA ASAL</t>
-  </si>
-  <si>
-    <t>KODE PERHITUNGAN</t>
-  </si>
-  <si>
-    <t>PERNYATAAN LARTAS</t>
-  </si>
-  <si>
-    <t>FLAG 4 TAHUN</t>
-  </si>
-  <si>
-    <t>SERI IZIN</t>
-  </si>
-  <si>
-    <t>TAHUN PEMBUATAN</t>
-  </si>
-  <si>
-    <t>KAPASITAS SILINDER</t>
-  </si>
-  <si>
-    <t>KODE BKC</t>
-  </si>
-  <si>
-    <t>KODE KOMODITI BKC</t>
-  </si>
-  <si>
-    <t>KODE SUB KOMODITI BKC</t>
-  </si>
-  <si>
-    <t>FLAG TIS</t>
-  </si>
-  <si>
-    <t>ISI PER KEMASAN</t>
-  </si>
-  <si>
-    <t>JUMLAH DILEKATKAN</t>
-  </si>
-  <si>
-    <t>JUMLAH PITA CUKAI</t>
-  </si>
-  <si>
-    <t>HJE CUKAI</t>
-  </si>
-  <si>
-    <t>TARIF CUKAI</t>
-  </si>
-  <si>
-    <t>METODE PENENTUAN NILAI</t>
-  </si>
-  <si>
-    <t>ALASAN METODE PENENTUAN NILAI</t>
-  </si>
-  <si>
-    <t>STATEMENT PERBEDAAN HARGA</t>
-  </si>
-  <si>
-    <t>61102000</t>
-  </si>
-  <si>
-    <t>KNM/0725/062</t>
-  </si>
-  <si>
-    <t>T-SHIRT SHORT SLEEVE
-PO : 60672678 S : 881293, OF GIRLS COTTON FIBERS, KNIT PULLOVER 60% COTTON 40% POLYESTER, COLOR : CALLA LILY 451</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>62101019</t>
+  </si>
+  <si>
+    <t>CBU/0925/021,020,019,016,022,015,023</t>
+  </si>
+  <si>
+    <t>AEZY REGULAR T-SHIRT (HASIL PERBAIKAN)</t>
   </si>
   <si>
     <t>PCE</t>
   </si>
   <si>
-    <t>3204</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>T-SHIRT SHORT SLEEVE
-PO : 60672676 S : 881293, OF GIRLS COTTON FIBERS, KNIT PULLOVER 60% COTTON 40% POLYESTER, COLOR : CALLA LILY 451</t>
-  </si>
-  <si>
     <t>KODE PUNGUTAN</t>
   </si>
   <si>
@@ -895,6 +878,39 @@
     <t>VALUTA</t>
   </si>
   <si>
+    <t>FABRIC KNIT SJ RY 401 COMPACT TUBULAR</t>
+  </si>
+  <si>
+    <t>10-23-2025 00:00:00</t>
+  </si>
+  <si>
+    <t>00004074540620251023005576</t>
+  </si>
+  <si>
+    <t>10-25-2025 00:00:00</t>
+  </si>
+  <si>
+    <t>00004074540620251025005671</t>
+  </si>
+  <si>
+    <t>61109000</t>
+  </si>
+  <si>
+    <t>AEZY T-SHIRT REGULAR (RETUR)</t>
+  </si>
+  <si>
+    <t>113145</t>
+  </si>
+  <si>
+    <t>10-13-2025 00:00:00</t>
+  </si>
+  <si>
+    <t>00004074540620251013005268</t>
+  </si>
+  <si>
+    <t>PPNLOKAL</t>
+  </si>
+  <si>
     <t>KODE_ASAL_BAHAN_BAKU</t>
   </si>
   <si>
@@ -925,12 +941,6 @@
     <t>NAMA</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>BANK BCA</t>
-  </si>
-  <si>
     <t>JENIS NILAI</t>
   </si>
   <si>
@@ -997,13 +1007,13 @@
     <t>TANGGAL RESPON</t>
   </si>
   <si>
-    <t>3015</t>
-  </si>
-  <si>
-    <t>670972/PM/KPU.1/2025</t>
-  </si>
-  <si>
-    <t>670831/PM/KPU.1/2025</t>
+    <t>4103</t>
+  </si>
+  <si>
+    <t>019548/KBC.0903/2025</t>
+  </si>
+  <si>
+    <t>019561/KBC.0903/2025</t>
   </si>
 </sst>
 </file>
@@ -1496,148 +1506,97 @@
       <c r="C2" t="s">
         <v>106</v>
       </c>
-      <c r="E2" t="s">
+      <c r="J2" t="s">
         <v>107</v>
       </c>
-      <c r="G2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="N2" t="s">
         <v>108</v>
       </c>
-      <c r="P2" t="s">
+      <c r="AB2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>1882.4</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>1882.4</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE2" t="s">
         <v>109</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="CF2" t="s">
         <v>110</v>
       </c>
-      <c r="W2" t="s">
+      <c r="CG2" t="s">
         <v>111</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="CH2" t="s">
         <v>112</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="CL2" t="s">
         <v>113</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="CM2" t="s">
+        <v>110</v>
+      </c>
+      <c r="CP2" t="s">
         <v>114</v>
       </c>
-      <c r="AR2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>117</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>288.84</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>761.94</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>16581.0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>37.06</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>33.06</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>120</v>
-      </c>
-      <c r="CF2" t="s">
-        <v>117</v>
-      </c>
-      <c r="CG2" t="s">
-        <v>121</v>
-      </c>
-      <c r="CH2" t="s">
-        <v>122</v>
-      </c>
-      <c r="CI2" t="s">
-        <v>123</v>
-      </c>
-      <c r="CJ2" t="s">
-        <v>124</v>
-      </c>
-      <c r="CO2" t="s">
-        <v>106</v>
-      </c>
-      <c r="CP2" t="s">
-        <v>125</v>
-      </c>
       <c r="CQ2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="CT2" t="n">
         <v>0.0</v>
       </c>
-      <c r="CZ2" t="s">
-        <v>126</v>
-      </c>
-      <c r="DB2" t="s">
-        <v>108</v>
+      <c r="CU2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>11.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
         <v>105</v>
@@ -1645,143 +1604,92 @@
       <c r="C3" t="s">
         <v>106</v>
       </c>
-      <c r="E3" t="s">
+      <c r="J3" t="s">
         <v>107</v>
       </c>
-      <c r="G3" t="s">
-        <v>106</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="N3" t="s">
         <v>108</v>
       </c>
-      <c r="P3" t="s">
+      <c r="AB3" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>341891.89</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>341891.89</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CE3" t="s">
         <v>109</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="CF3" t="s">
         <v>110</v>
       </c>
-      <c r="W3" t="s">
+      <c r="CG3" t="s">
         <v>111</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="CH3" t="s">
         <v>112</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="CL3" t="s">
         <v>113</v>
       </c>
-      <c r="AO3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV3" t="s">
+      <c r="CM3" t="s">
+        <v>110</v>
+      </c>
+      <c r="CP3" t="s">
         <v>116</v>
       </c>
-      <c r="AZ3" t="s">
-        <v>117</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>118</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>119</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>957.58</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>2526.03</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>16581.0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>119.77</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>109.67</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>120</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>117</v>
-      </c>
-      <c r="CG3" t="s">
-        <v>121</v>
-      </c>
-      <c r="CH3" t="s">
-        <v>122</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>123</v>
-      </c>
-      <c r="CJ3" t="s">
-        <v>124</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>106</v>
-      </c>
-      <c r="CP3" t="s">
-        <v>128</v>
-      </c>
       <c r="CQ3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="CZ3" t="s">
-        <v>126</v>
-      </c>
-      <c r="DB3" t="s">
-        <v>108</v>
+        <v>37608.11</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>11.0</v>
       </c>
     </row>
   </sheetData>
@@ -1813,13 +1721,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -1850,10 +1758,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -1883,13 +1791,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -1923,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>61</v>
@@ -1938,7 +1846,7 @@
         <v>67</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -1959,11 +1867,13 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="38.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1973,7 +1883,7 @@
     <col min="17" max="17" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="18.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="11.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -1996,64 +1906,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="P1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>77</v>
@@ -2068,52 +1978,301 @@
         <v>69</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AE1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="AH1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L2" t="s">
+        <v>256</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1338.35</v>
+      </c>
+      <c r="P2" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>106</v>
+      </c>
+      <c r="R2" t="s">
+        <v>168</v>
+      </c>
+      <c r="S2" t="s">
+        <v>282</v>
+      </c>
+      <c r="T2" t="s">
         <v>283</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="AO1" s="1" t="s">
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2485.85</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" t="s">
         <v>253</v>
+      </c>
+      <c r="F3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" t="s">
+        <v>281</v>
+      </c>
+      <c r="H3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K3" t="s">
+        <v>113</v>
+      </c>
+      <c r="L3" t="s">
+        <v>256</v>
+      </c>
+      <c r="M3" t="n">
+        <v>544.05</v>
+      </c>
+      <c r="P3" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>106</v>
+      </c>
+      <c r="R3" t="s">
+        <v>172</v>
+      </c>
+      <c r="S3" t="s">
+        <v>284</v>
+      </c>
+      <c r="T3" t="s">
+        <v>285</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1111.55</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" t="s">
+        <v>286</v>
+      </c>
+      <c r="F4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" t="s">
+        <v>287</v>
+      </c>
+      <c r="H4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I4" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K4" t="s">
+        <v>113</v>
+      </c>
+      <c r="L4" t="s">
+        <v>261</v>
+      </c>
+      <c r="M4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>106</v>
+      </c>
+      <c r="R4" t="s">
+        <v>288</v>
+      </c>
+      <c r="S4" t="s">
+        <v>289</v>
+      </c>
+      <c r="T4" t="s">
+        <v>290</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2134,7 +2293,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2165,76 +2324,208 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="T1" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>256</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1338.35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M3" t="s">
+        <v>256</v>
+      </c>
+      <c r="N3" t="n">
+        <v>544.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M4" t="s">
+        <v>261</v>
+      </c>
+      <c r="N4" t="n">
+        <v>33.0</v>
       </c>
     </row>
   </sheetData>
@@ -2268,19 +2559,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -2313,16 +2604,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2363,28 +2654,28 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -2405,8 +2696,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2414,41 +2704,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>294</v>
-      </c>
-      <c r="D2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -2474,11 +2736,11 @@
     <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="23.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="24.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="120.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="98.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="19.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2491,49 +2753,49 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2">
@@ -2541,22 +2803,31 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="F2" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="G2" t="s">
-        <v>153</v>
+        <v>140</v>
+      </c>
+      <c r="H2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" t="s">
+        <v>142</v>
+      </c>
+      <c r="L2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="3">
@@ -2564,19 +2835,28 @@
         <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>144</v>
+      </c>
+      <c r="D3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E3" t="s">
+        <v>145</v>
       </c>
       <c r="F3" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G3" t="s">
-        <v>155</v>
-      </c>
-      <c r="M3" t="s">
-        <v>113</v>
+        <v>147</v>
+      </c>
+      <c r="I3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J3" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="4">
@@ -2584,204 +2864,118 @@
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C4" t="s">
-        <v>156</v>
+        <v>150</v>
+      </c>
+      <c r="D4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E4" t="s">
+        <v>145</v>
       </c>
       <c r="F4" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="G4" t="s">
-        <v>158</v>
-      </c>
-      <c r="M4" t="s">
-        <v>113</v>
+        <v>147</v>
+      </c>
+      <c r="I4" t="s">
+        <v>148</v>
+      </c>
+      <c r="J4" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="F5" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="G5" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="H5" t="s">
-        <v>162</v>
-      </c>
-      <c r="J5" t="s">
-        <v>163</v>
+        <v>141</v>
+      </c>
+      <c r="K5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L5" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="F6" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="G6" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="I6" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="J6" t="s">
-        <v>169</v>
-      </c>
-      <c r="O6" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>150</v>
+      </c>
+      <c r="D7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" t="s">
+        <v>152</v>
       </c>
       <c r="F7" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="G7" t="s">
-        <v>171</v>
-      </c>
-      <c r="M7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G8" t="s">
-        <v>161</v>
-      </c>
-      <c r="H8" t="s">
-        <v>162</v>
-      </c>
-      <c r="J8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F9" t="s">
-        <v>166</v>
-      </c>
-      <c r="G9" t="s">
-        <v>167</v>
-      </c>
-      <c r="I9" t="s">
-        <v>168</v>
-      </c>
-      <c r="J9" t="s">
-        <v>169</v>
-      </c>
-      <c r="O9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I7" t="s">
         <v>148</v>
       </c>
-      <c r="C10" t="s">
+      <c r="J7" t="s">
         <v>149</v>
-      </c>
-      <c r="D10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E10" t="s">
-        <v>151</v>
-      </c>
-      <c r="F10" t="s">
-        <v>152</v>
-      </c>
-      <c r="G10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" t="s">
-        <v>112</v>
-      </c>
-      <c r="F11" t="s">
-        <v>154</v>
-      </c>
-      <c r="G11" t="s">
-        <v>155</v>
-      </c>
-      <c r="M11" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2804,12 +2998,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -2841,41 +3035,41 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="D1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2898,7 +3092,7 @@
   <cols>
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="21.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="57.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="16.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="10.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -2909,22 +3103,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2">
@@ -2935,13 +3129,13 @@
         <v>1.0</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
@@ -2952,13 +3146,13 @@
         <v>2.0</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4">
@@ -2969,13 +3163,13 @@
         <v>3.0</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5">
@@ -2986,81 +3180,132 @@
         <v>4.0</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D5" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="E5" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B6" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B7" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="C7" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D7" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B8" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="C8" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="D8" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" t="n">
         <v>4.0</v>
       </c>
-      <c r="C9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E12" t="s">
         <v>182</v>
-      </c>
-      <c r="E9" t="s">
-        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3096,28 +3341,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="2">
@@ -3127,37 +3372,25 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>108</v>
-      </c>
       <c r="D2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F2" t="s">
-        <v>194</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>108</v>
-      </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F3" t="s">
-        <v>194</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -3181,7 +3414,6 @@
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3189,16 +3421,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2">
@@ -3209,30 +3441,24 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>199</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>199</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3265,19 +3491,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3319,61 +3545,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>60</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2">
@@ -3381,7 +3607,7 @@
         <v>104</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C2" t="n">
         <v>0.0</v>
@@ -3440,7 +3666,7 @@
         <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C3" t="n">
         <v>0.0</v>
@@ -3496,7 +3722,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
         <v>108</v>
@@ -3555,10 +3781,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C5" t="n">
         <v>0.0</v>
@@ -3633,9 +3859,8 @@
     <col min="1" max="1" width="27.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="134.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="9.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="37.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="46.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="17.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="12.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="14.42578125" outlineLevel="0" customWidth="true" bestFit="true"/>
@@ -3697,58 +3922,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>77</v>
@@ -3760,19 +3985,19 @@
         <v>78</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>69</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>71</v>
@@ -3787,25 +4012,25 @@
         <v>64</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="AM1" s="1" t="s">
         <v>61</v>
@@ -3814,94 +4039,94 @@
         <v>74</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>88</v>
       </c>
       <c r="AV1" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2">
@@ -3912,135 +4137,132 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J2" t="s">
+        <v>256</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1882.4</v>
+      </c>
+      <c r="L2" t="s">
+        <v>194</v>
+      </c>
+      <c r="M2" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1882.4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>107</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="BR2" t="s">
         <v>257</v>
-      </c>
-      <c r="D2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G2" t="s">
-        <v>260</v>
-      </c>
-      <c r="H2" t="s">
-        <v>260</v>
-      </c>
-      <c r="I2" t="s">
-        <v>260</v>
-      </c>
-      <c r="J2" t="s">
-        <v>261</v>
-      </c>
-      <c r="K2" t="n">
-        <v>498.0</v>
-      </c>
-      <c r="L2" t="s">
-        <v>198</v>
-      </c>
-      <c r="M2" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>33.06</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>16581.0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>761.94</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>262</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>263</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>108</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F3" t="s">
-        <v>199</v>
+        <v>113</v>
       </c>
       <c r="G3" t="s">
-        <v>260</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
-        <v>260</v>
+        <v>113</v>
       </c>
       <c r="I3" t="s">
-        <v>260</v>
+        <v>113</v>
       </c>
       <c r="J3" t="s">
         <v>261</v>
       </c>
       <c r="K3" t="n">
-        <v>1651.0</v>
+        <v>33.0</v>
       </c>
       <c r="L3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M3" t="n">
-        <v>11.0</v>
+        <v>18.0</v>
       </c>
       <c r="T3" t="n">
-        <v>109.67</v>
+        <v>7.0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.0</v>
       </c>
       <c r="Z3" t="n">
         <v>0.0</v>
@@ -4049,10 +4271,10 @@
         <v>0.0</v>
       </c>
       <c r="AB3" t="n">
-        <v>16581.0</v>
+        <v>0.0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2526.03</v>
+        <v>0.0</v>
       </c>
       <c r="AF3" t="n">
         <v>0.0</v>
@@ -4061,14 +4283,11 @@
         <v>0.0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0</v>
+        <v>341891.89</v>
       </c>
       <c r="AI3" t="n">
         <v>0.0</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AK3" t="n">
         <v>0.0</v>
       </c>
@@ -4078,20 +4297,14 @@
       <c r="AN3" t="n">
         <v>0.0</v>
       </c>
-      <c r="AS3" t="s">
-        <v>262</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>263</v>
+      <c r="AW3" t="s">
+        <v>107</v>
       </c>
       <c r="BJ3" t="n">
         <v>0.0</v>
       </c>
-      <c r="BO3" t="s">
-        <v>108</v>
-      </c>
       <c r="BR3" t="s">
-        <v>126</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4137,58 +4350,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
